--- a/Defect_Tracker_v0.1.xlsx
+++ b/Defect_Tracker_v0.1.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -911,6 +911,177 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>Resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CORS preflight request blocked on authentication and submission endpoints.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Network/CORS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Configured allow_origin_regex in FastAPI main.py. Verified HTTP 200 OK for CORS preflight.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Resolved &amp; Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Markdown and JSON export formats were missing from Code Review Report Generator.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Feature Enhancement</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Implemented generate_submission_markdown and generate_submission_json methods in report_generator.py and added API endpoints.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>07-08-2026</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Fully Operational</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>07-08-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>User Dashboard navigation button hidden for unauthenticated users.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Frontend/UI</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Updated page.tsx top navigation header so User Dashboard button is always visible and opens auth modal if logged out.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>07-08-2026</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
     </row>

--- a/Defect_Tracker_v0.1.xlsx
+++ b/Defect_Tracker_v0.1.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Defects" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Defects'!$A$1:$K$8</definedName>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +38,19 @@
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,8 +63,20 @@
         <bgColor rgb="003B71CA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -76,11 +98,25 @@
         <color rgb="00C0C0C0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -90,6 +126,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -459,627 +510,627 @@
   <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Sl No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Submitted By</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Submitted Date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Detected Sprint</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Assigned To</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Type Of Defect</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Action Taken</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Action Taken Date</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="2" t="n">
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>08-07-2026</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Duplicate submission API routes registered in FastAPI backend router.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Removed redundant duplicate router endpoints in main.py.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>09-07-2026</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>Verified successfully</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="2" t="n">
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>10-07-2026</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Frontend Next.js client failed to connect to backend due to port 8000 server downtime.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>Launched Uvicorn backend process on port 8000 and verified backend health.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>11-07-2026</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Server Active</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="n">
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>13-07-2026</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Anthropic dependency removed from multi-agent pipeline.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Migrated multi-agent orchestrator and models to Google Gemini API.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>15-07-2026</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>API updated</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="2" t="n">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>16-07-2026</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Flask and required modules missing in virtual environment during setup.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Installed missing dependencies into backend virtual environment.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>16-07-2026</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="2" t="n">
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>18-07-2026</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Gemini API key failing to load from environment configuration.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Added dotenv loading in config.py and validated API key initialization.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>19-07-2026</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>Working</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="2" t="n">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>21-07-2026</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>RAG Knowledge Base search threw 'Failed to fetch' error when querying vector DB.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Network/Backend</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Resolved backend server connection refused error and initialized ChromaDB vector store.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>24-07-2026</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>Fully Operational</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="2" t="n">
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>24-07-2026</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Browser reported ERR_CONNECTION_REFUSED when accessing localhost:3000.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Started Next.js dev server (npm run dev) on port 3000.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>24-07-2026</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>05-08-2026</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>CORS preflight request blocked on authentication and submission endpoints.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>Network/CORS</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Configured allow_origin_regex in FastAPI main.py. Verified HTTP 200 OK for CORS preflight.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>06-08-2026</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>Resolved &amp; Active</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>06-08-2026</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Markdown and JSON export formats were missing from Code Review Report Generator.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Feature Enhancement</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Implemented generate_submission_markdown and generate_submission_json methods in report_generator.py and added API endpoints.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>07-08-2026</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>Fully Operational</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>07-08-2026</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>User Dashboard navigation button hidden for unauthenticated users.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>Frontend/UI</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Updated page.tsx top navigation header so User Dashboard button is always visible and opens auth modal if logged out.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>07-08-2026</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
@@ -1089,17 +1140,4 @@
   <autoFilter ref="A1:K8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/Defect_Tracker_v0.1.xlsx
+++ b/Defect_Tracker_v0.1.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>20-07-2026</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>21-07-2026</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>25-07-2026</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>27-07-2026</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>28-07-2026</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">

--- a/Defect_Tracker_v0.1.xlsx
+++ b/Defect_Tracker_v0.1.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>20-07-2026</t>
+          <t>28-07-2026</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>21-07-2026</t>
+          <t>29-07-2026</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>25-07-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>27-07-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>28-07-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">

--- a/Defect_Tracker_v0.1.xlsx
+++ b/Defect_Tracker_v0.1.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1136,6 +1136,177 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>29-07-2026</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>JWT authentication token missing from Authorization header in dashboard API calls.</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Updated api.ts client to inject Bearer token in request headers.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>30-07-2026</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>Resolved &amp; Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>02-08-2026</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Line number highlighting offset by 1 on code viewer component.</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Frontend/UI</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Adjusted 1-based indexing in line highlight lookup mapping.</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>03-08-2026</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>07-08-2026</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>PDF Report generator title text overlap on multiline headers.</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Configured explicit fontSize=16 and leading=20 in ReportGenerator title_style.</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>07-08-2026</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>Fixed &amp; Verified</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Defect_Tracker_v0.1.xlsx
+++ b/Defect_Tracker_v0.1.xlsx
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -141,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,20 +513,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -581,729 +587,949 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>08-07-2026</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Duplicate submission API routes registered in FastAPI backend router.</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>Removed redundant duplicate router endpoints in main.py.</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>09-07-2026</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K2" s="10" t="inlineStr">
         <is>
           <t>Verified successfully</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>10-07-2026</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Frontend Next.js client failed to connect to backend due to port 8000 server downtime.</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>Launched Uvicorn backend process on port 8000 and verified backend health.</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>11-07-2026</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>Server Active</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>13-07-2026</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Anthropic dependency removed from multi-agent pipeline.</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Migrated multi-agent orchestrator and models to Google Gemini API.</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>15-07-2026</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>API updated</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>16-07-2026</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Flask and required modules missing in virtual environment during setup.</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Installed missing dependencies into backend virtual environment.</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>16-07-2026</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>18-07-2026</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Gemini API key failing to load from environment configuration.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Added dotenv loading in config.py and validated API key initialization.</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>19-07-2026</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>Working</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>21-07-2026</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>RAG Knowledge Base search threw 'Failed to fetch' error when querying vector DB.</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Network/Backend</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>Resolved backend server connection refused error and initialized ChromaDB vector store.</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>24-07-2026</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>Fully Operational</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>24-07-2026</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Browser reported ERR_CONNECTION_REFUSED when accessing localhost:3000.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Started Next.js dev server (npm run dev) on port 3000.</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>24-07-2026</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>28-07-2026</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>CORS preflight request blocked on authentication and submission endpoints.</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Network/CORS</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Configured allow_origin_regex in FastAPI main.py. Verified HTTP 200 OK for CORS preflight.</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>29-07-2026</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>Resolved &amp; Active</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>03-08-2026</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Markdown and JSON export formats were missing from Code Review Report Generator.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Feature Enhancement</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Implemented generate_submission_markdown and generate_submission_json methods in report_generator.py and added API endpoints.</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>04-08-2026</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>Fully Operational</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>06-08-2026</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>User Dashboard navigation button hidden for unauthenticated users.</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Frontend/UI</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Updated page.tsx top navigation header so User Dashboard button is always visible and opens auth modal if logged out.</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>07-08-2026</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>29-07-2026</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>JWT authentication token missing from Authorization header in dashboard API calls.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Authentication</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>Updated api.ts client to inject Bearer token in request headers.</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>30-07-2026</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
         <is>
           <t>Resolved &amp; Verified</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>02-08-2026</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>Line number highlighting offset by 1 on code viewer component.</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Frontend/UI</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Adjusted 1-based indexing in line highlight lookup mapping.</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>03-08-2026</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>07-08-2026</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>PDF Report generator title text overlap on multiline headers.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>Thimmampalli Asritha</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Configured explicit fontSize=16 and leading=20 in ReportGenerator title_style.</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>07-08-2026</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
         <is>
           <t>Fixed &amp; Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>10-08-2026</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>LLM remediation generated non-compilable AST return statements in complex Java methods.</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Code Generation</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Implemented AST-level Post-Generation Remediation Validator with fallback engine.</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>12-08-2026</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>Verified &amp; Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>14-08-2026</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>PR Summary view lacked visual side-by-side diff between original vulnerable code and remediated code.</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>UI Enhancement</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>Integrated CodeDiffViewer component with unified and side-by-side view toggles.</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>15-08-2026</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>16-08-2026</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Security policy scanner module toggles did not persist or dynamically update portal findings count.</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Frontend/State</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Wired active security policy context to real-time finding filters across all portal tabs.</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>16-08-2026</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Project documentation, backend API, report generator, and frontend UI had legacy project title.</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Thimmampalli Asritha</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Documentation/Branding</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Updated project title to 'Development of Smart Code Inspection Platform with Vulnerability Detection System Group 2' and added MIT License.</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
     </row>

--- a/Defect_Tracker_v0.1.xlsx
+++ b/Defect_Tracker_v0.1.xlsx
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -146,6 +146,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -516,78 +519,78 @@
   <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Sl No</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Submitted By</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Submitted Date</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Detected Sprint</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Assigned To</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Type Of Defect</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Action Taken</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Action Taken Date</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="10" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="inlineStr">
@@ -595,7 +598,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>08-07-2026</t>
         </is>
@@ -605,7 +608,7 @@
           <t>Duplicate submission API routes registered in FastAPI backend router.</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
@@ -625,12 +628,12 @@
           <t>Removed redundant duplicate router endpoints in main.py.</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>09-07-2026</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -642,7 +645,7 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="10" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="inlineStr">
@@ -650,7 +653,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>10-07-2026</t>
         </is>
@@ -660,7 +663,7 @@
           <t>Frontend Next.js client failed to connect to backend due to port 8000 server downtime.</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
@@ -680,12 +683,12 @@
           <t>Launched Uvicorn backend process on port 8000 and verified backend health.</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>11-07-2026</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -697,7 +700,7 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="10" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -705,7 +708,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>13-07-2026</t>
         </is>
@@ -715,7 +718,7 @@
           <t>Anthropic dependency removed from multi-agent pipeline.</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
@@ -735,12 +738,12 @@
           <t>Migrated multi-agent orchestrator and models to Google Gemini API.</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>15-07-2026</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -752,7 +755,7 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="10" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -760,7 +763,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>16-07-2026</t>
         </is>
@@ -770,7 +773,7 @@
           <t>Flask and required modules missing in virtual environment during setup.</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
@@ -790,12 +793,12 @@
           <t>Installed missing dependencies into backend virtual environment.</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>16-07-2026</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -807,7 +810,7 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="10" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -815,7 +818,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>18-07-2026</t>
         </is>
@@ -825,7 +828,7 @@
           <t>Gemini API key failing to load from environment configuration.</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
@@ -845,12 +848,12 @@
           <t>Added dotenv loading in config.py and validated API key initialization.</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>19-07-2026</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -862,7 +865,7 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="10" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -870,7 +873,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>21-07-2026</t>
         </is>
@@ -880,7 +883,7 @@
           <t>RAG Knowledge Base search threw 'Failed to fetch' error when querying vector DB.</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
@@ -900,12 +903,12 @@
           <t>Resolved backend server connection refused error and initialized ChromaDB vector store.</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>24-07-2026</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -917,7 +920,7 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="10" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -925,7 +928,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>24-07-2026</t>
         </is>
@@ -935,7 +938,7 @@
           <t>Browser reported ERR_CONNECTION_REFUSED when accessing localhost:3000.</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
@@ -955,12 +958,12 @@
           <t>Started Next.js dev server (npm run dev) on port 3000.</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>24-07-2026</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -972,7 +975,7 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -982,7 +985,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>28-07-2026</t>
         </is>
@@ -992,7 +995,7 @@
           <t>CORS preflight request blocked on authentication and submission endpoints.</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
@@ -1012,12 +1015,12 @@
           <t>Configured allow_origin_regex in FastAPI main.py. Verified HTTP 200 OK for CORS preflight.</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>29-07-2026</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -1029,7 +1032,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1039,7 +1042,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>03-08-2026</t>
         </is>
@@ -1049,7 +1052,7 @@
           <t>Markdown and JSON export formats were missing from Code Review Report Generator.</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
@@ -1069,12 +1072,12 @@
           <t>Implemented generate_submission_markdown and generate_submission_json methods in report_generator.py and added API endpoints.</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>04-08-2026</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -1086,7 +1089,7 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1096,7 +1099,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>06-08-2026</t>
         </is>
@@ -1106,7 +1109,7 @@
           <t>User Dashboard navigation button hidden for unauthenticated users.</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
@@ -1126,12 +1129,12 @@
           <t>Updated page.tsx top navigation header so User Dashboard button is always visible and opens auth modal if logged out.</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>07-08-2026</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -1143,7 +1146,7 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1153,7 +1156,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>29-07-2026</t>
         </is>
@@ -1163,7 +1166,7 @@
           <t>JWT authentication token missing from Authorization header in dashboard API calls.</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
@@ -1183,12 +1186,12 @@
           <t>Updated api.ts client to inject Bearer token in request headers.</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>30-07-2026</t>
         </is>
       </c>
-      <c r="J12" s="9" t="inlineStr">
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -1200,7 +1203,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1210,7 +1213,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>02-08-2026</t>
         </is>
@@ -1220,7 +1223,7 @@
           <t>Line number highlighting offset by 1 on code viewer component.</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
@@ -1240,12 +1243,12 @@
           <t>Adjusted 1-based indexing in line highlight lookup mapping.</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>03-08-2026</t>
         </is>
       </c>
-      <c r="J13" s="9" t="inlineStr">
+      <c r="J13" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -1257,7 +1260,7 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1267,7 +1270,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>07-08-2026</t>
         </is>
@@ -1277,7 +1280,7 @@
           <t>PDF Report generator title text overlap on multiline headers.</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
@@ -1297,12 +1300,12 @@
           <t>Configured explicit fontSize=16 and leading=20 in ReportGenerator title_style.</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>07-08-2026</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -1314,7 +1317,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="10" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1322,7 +1325,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>10-08-2026</t>
         </is>
@@ -1332,7 +1335,7 @@
           <t>LLM remediation generated non-compilable AST return statements in complex Java methods.</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
@@ -1352,12 +1355,12 @@
           <t>Implemented AST-level Post-Generation Remediation Validator with fallback engine.</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>12-08-2026</t>
         </is>
       </c>
-      <c r="J15" s="9" t="inlineStr">
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -1369,7 +1372,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n">
+      <c r="A16" s="10" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1377,7 +1380,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>14-08-2026</t>
         </is>
@@ -1387,7 +1390,7 @@
           <t>PR Summary view lacked visual side-by-side diff between original vulnerable code and remediated code.</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
@@ -1407,12 +1410,12 @@
           <t>Integrated CodeDiffViewer component with unified and side-by-side view toggles.</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>15-08-2026</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="J16" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -1424,7 +1427,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n">
+      <c r="A17" s="10" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1432,7 +1435,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>16-08-2026</t>
         </is>
@@ -1442,7 +1445,7 @@
           <t>Security policy scanner module toggles did not persist or dynamically update portal findings count.</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
@@ -1462,12 +1465,12 @@
           <t>Wired active security policy context to real-time finding filters across all portal tabs.</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>16-08-2026</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -1479,7 +1482,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n">
+      <c r="A18" s="10" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -1487,7 +1490,7 @@
           <t>Thimmampalli Asritha</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>17-08-2026</t>
         </is>
@@ -1497,7 +1500,7 @@
           <t>Project documentation, backend API, report generator, and frontend UI had legacy project title.</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
@@ -1517,12 +1520,12 @@
           <t>Updated project title to 'Development of Smart Code Inspection Platform with Vulnerability Detection System Group 2' and added MIT License.</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>17-08-2026</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="J18" s="10" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
